--- a/เทมเพลตนำเข้ารายชื่อนักเรียน_คลินิกวิชาการ (2).csv.xlsx
+++ b/เทมเพลตนำเข้ารายชื่อนักเรียน_คลินิกวิชาการ (2).csv.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ทำเวปคลีนิควิชาการ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{563688C4-4FA8-4583-A6C6-B1731982BA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898097AC-9184-4682-9BAB-03AED87A5566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9600" yWindow="1747" windowWidth="12743" windowHeight="12323" xr2:uid="{D37474B6-41D1-4A73-8E2B-A2A3278FB992}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" activeTab="1" xr2:uid="{D37474B6-41D1-4A73-8E2B-A2A3278FB992}"/>
   </bookViews>
   <sheets>
     <sheet name="เทมเพลตนำเข้ารายชื่อนักเรียน_คล" sheetId="1" r:id="rId1"/>
+    <sheet name="34" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="919">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="967">
   <si>
     <t>รหัสประจำตัว</t>
   </si>
@@ -2788,6 +2789,150 @@
   </si>
   <si>
     <t>อรศศิวรรณ์ อรรถสถาวร</t>
+  </si>
+  <si>
+    <t>05936</t>
+  </si>
+  <si>
+    <t>05937</t>
+  </si>
+  <si>
+    <t>05938</t>
+  </si>
+  <si>
+    <t>05939</t>
+  </si>
+  <si>
+    <t>05940</t>
+  </si>
+  <si>
+    <t>05941</t>
+  </si>
+  <si>
+    <t>05942</t>
+  </si>
+  <si>
+    <t>05943</t>
+  </si>
+  <si>
+    <t>05944</t>
+  </si>
+  <si>
+    <t>05945</t>
+  </si>
+  <si>
+    <t>05946</t>
+  </si>
+  <si>
+    <t>05947</t>
+  </si>
+  <si>
+    <t>05948</t>
+  </si>
+  <si>
+    <t>05949</t>
+  </si>
+  <si>
+    <t>05950</t>
+  </si>
+  <si>
+    <t>05951</t>
+  </si>
+  <si>
+    <t>05952</t>
+  </si>
+  <si>
+    <t>05953</t>
+  </si>
+  <si>
+    <t>05954</t>
+  </si>
+  <si>
+    <t>05955</t>
+  </si>
+  <si>
+    <t>05956</t>
+  </si>
+  <si>
+    <t>05957</t>
+  </si>
+  <si>
+    <t>05958</t>
+  </si>
+  <si>
+    <t>05959</t>
+  </si>
+  <si>
+    <t>กษิดิศ แดงอุบล</t>
+  </si>
+  <si>
+    <t>จิรัฏฐ์ นาวายนต์</t>
+  </si>
+  <si>
+    <t>ชิณธรรม ทองเสทื้อน</t>
+  </si>
+  <si>
+    <t>ณัฐภาส บูรณมานัส</t>
+  </si>
+  <si>
+    <t>ดิศธรรม สุวรรณมโหสถ</t>
+  </si>
+  <si>
+    <t>เตชินท์ ขันตี</t>
+  </si>
+  <si>
+    <t>ธนาคิม ชนิดไทย</t>
+  </si>
+  <si>
+    <t>นนทพัทธ์ กบิลพัฒน์</t>
+  </si>
+  <si>
+    <t>พิสิทธิ์ บุญมี</t>
+  </si>
+  <si>
+    <t>ภคพล อินทปัตย์</t>
+  </si>
+  <si>
+    <t>ภาคิน โชติมณี</t>
+  </si>
+  <si>
+    <t>วิชญะ ธรรมวิชุกร</t>
+  </si>
+  <si>
+    <t>สิรชัจพิชญ์ วรรณนรันทร์</t>
+  </si>
+  <si>
+    <t>กิ่งเพชร แต่สกุล</t>
+  </si>
+  <si>
+    <t>เขมจิรา จงกลกลาง</t>
+  </si>
+  <si>
+    <t>ณิชนันทน์ พุ่มพินิจ</t>
+  </si>
+  <si>
+    <t>ธัญญาพร สุขศิริ</t>
+  </si>
+  <si>
+    <t>ธัญสรณ์ เกิดเขาทะลุ</t>
+  </si>
+  <si>
+    <t>น้ำทิพย์ หวายลี</t>
+  </si>
+  <si>
+    <t>เบญริสา พร้อมทวีพงศ์</t>
+  </si>
+  <si>
+    <t>พิรดาภร เงาดำ</t>
+  </si>
+  <si>
+    <t>สิริกร พรจรรยา</t>
+  </si>
+  <si>
+    <t>สุทธินันท์ สุขธรรม</t>
+  </si>
+  <si>
+    <t>แองเจลีน่า กาญ่า หมื่นชัยพรหม</t>
   </si>
 </sst>
 </file>
@@ -17652,4 +17797,494 @@
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CFB9ECC-CC09-4D77-9B6F-CAD0F35D70F1}">
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:7" ht="20.65" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>919</v>
+      </c>
+      <c r="B1" t="s">
+        <v>943</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>1</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="20.65" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>920</v>
+      </c>
+      <c r="B2" t="s">
+        <v>944</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="20.65" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>921</v>
+      </c>
+      <c r="B3" t="s">
+        <v>945</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="20.65" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>922</v>
+      </c>
+      <c r="B4" t="s">
+        <v>946</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="20.65" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>923</v>
+      </c>
+      <c r="B5" t="s">
+        <v>947</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="20.65" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>924</v>
+      </c>
+      <c r="B6" t="s">
+        <v>948</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="20.65" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>925</v>
+      </c>
+      <c r="B7" t="s">
+        <v>949</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="20.65" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>926</v>
+      </c>
+      <c r="B8" t="s">
+        <v>950</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>8</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="20.65" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>927</v>
+      </c>
+      <c r="B9" t="s">
+        <v>951</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9">
+        <v>9</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="20.65" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>928</v>
+      </c>
+      <c r="B10" t="s">
+        <v>952</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>4</v>
+      </c>
+      <c r="F10">
+        <v>10</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="20.65" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>929</v>
+      </c>
+      <c r="B11" t="s">
+        <v>953</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+      <c r="F11">
+        <v>11</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="20.65" x14ac:dyDescent="0.35">
+      <c r="A12" s="5" t="s">
+        <v>930</v>
+      </c>
+      <c r="B12" t="s">
+        <v>954</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12">
+        <v>4</v>
+      </c>
+      <c r="F12">
+        <v>12</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="20.65" x14ac:dyDescent="0.35">
+      <c r="A13" s="5" t="s">
+        <v>931</v>
+      </c>
+      <c r="B13" t="s">
+        <v>955</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13">
+        <v>4</v>
+      </c>
+      <c r="F13">
+        <v>13</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="20.65" x14ac:dyDescent="0.35">
+      <c r="A14" s="5" t="s">
+        <v>932</v>
+      </c>
+      <c r="B14" t="s">
+        <v>956</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14">
+        <v>4</v>
+      </c>
+      <c r="F14">
+        <v>14</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="20.65" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="s">
+        <v>933</v>
+      </c>
+      <c r="B15" t="s">
+        <v>957</v>
+      </c>
+      <c r="D15">
+        <v>3</v>
+      </c>
+      <c r="E15">
+        <v>4</v>
+      </c>
+      <c r="F15">
+        <v>15</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="20.65" x14ac:dyDescent="0.35">
+      <c r="A16" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="B16" t="s">
+        <v>958</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+      <c r="F16">
+        <v>16</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="20.65" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="s">
+        <v>935</v>
+      </c>
+      <c r="B17" t="s">
+        <v>959</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+      <c r="F17">
+        <v>17</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="20.65" x14ac:dyDescent="0.35">
+      <c r="A18" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="B18" t="s">
+        <v>960</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
+      <c r="F18">
+        <v>18</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="20.65" x14ac:dyDescent="0.35">
+      <c r="A19" s="5" t="s">
+        <v>937</v>
+      </c>
+      <c r="B19" t="s">
+        <v>961</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19">
+        <v>4</v>
+      </c>
+      <c r="F19">
+        <v>19</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="20.65" x14ac:dyDescent="0.35">
+      <c r="A20" s="5" t="s">
+        <v>938</v>
+      </c>
+      <c r="B20" t="s">
+        <v>962</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20">
+        <v>4</v>
+      </c>
+      <c r="F20">
+        <v>20</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="20.65" x14ac:dyDescent="0.35">
+      <c r="A21" s="5" t="s">
+        <v>939</v>
+      </c>
+      <c r="B21" t="s">
+        <v>963</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21">
+        <v>4</v>
+      </c>
+      <c r="F21">
+        <v>21</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="20.65" x14ac:dyDescent="0.35">
+      <c r="A22" s="5" t="s">
+        <v>940</v>
+      </c>
+      <c r="B22" t="s">
+        <v>964</v>
+      </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+      <c r="E22">
+        <v>4</v>
+      </c>
+      <c r="F22">
+        <v>22</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="20.65" x14ac:dyDescent="0.35">
+      <c r="A23" s="5" t="s">
+        <v>941</v>
+      </c>
+      <c r="B23" t="s">
+        <v>965</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="F23">
+        <v>23</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="20.65" x14ac:dyDescent="0.35">
+      <c r="A24" s="5" t="s">
+        <v>942</v>
+      </c>
+      <c r="B24" t="s">
+        <v>966</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24">
+        <v>4</v>
+      </c>
+      <c r="F24">
+        <v>24</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>